--- a/tools/importer/reports/import-procedure-detail.report.xlsx
+++ b/tools/importer/reports/import-procedure-detail.report.xlsx
@@ -125,7 +125,7 @@
     <t>procedure-detail</t>
   </si>
   <si>
-    <t>2026-09-10T08:33:56.134Z</t>
+    <t>2026-09-11T11:40:17.149Z</t>
   </si>
   <si>
     <t>Balloon kyphoplasty | Interventional Spine | Stryker</t>
@@ -137,7 +137,7 @@
     <t>us/en/ivs/treatments/bone-tumor-ablation</t>
   </si>
   <si>
-    <t>2026-09-10T08:39:05.525Z</t>
+    <t>2026-09-11T11:44:11.639Z</t>
   </si>
   <si>
     <t>Bone tumor ablation | Interventional Spine | Stryker</t>
@@ -172,7 +172,7 @@
     <t>us/en/ivs/treatments/disc-decompression</t>
   </si>
   <si>
-    <t>2026-09-10T08:36:00.526Z</t>
+    <t>2026-09-11T11:41:55.309Z</t>
   </si>
   <si>
     <t>Disc decompression | Interventional Spine | Stryker</t>
@@ -184,7 +184,7 @@
     <t>us/en/ivs/treatments/radiofrequency-ablation</t>
   </si>
   <si>
-    <t>2026-09-10T08:38:03.526Z</t>
+    <t>2026-09-11T11:43:55.708Z</t>
   </si>
   <si>
     <t>Radiofrequency ablation | Interventional Spine | Stryker</t>
@@ -214,7 +214,7 @@
     <t>us/en/ivs/treatments/sacroplasty</t>
   </si>
   <si>
-    <t>2026-09-10T08:40:06.327Z</t>
+    <t>2026-09-11T11:44:28.338Z</t>
   </si>
   <si>
     <t>Sacroplasty | Interventional Spine | Stryker</t>
@@ -226,7 +226,7 @@
     <t>us/en/ivs/treatments/spinejack-system</t>
   </si>
   <si>
-    <t>2026-09-10T08:37:03.028Z</t>
+    <t>2026-09-11T11:42:55.503Z</t>
   </si>
   <si>
     <t>SpineJack system | Interventional Spine | Stryker</t>
@@ -244,7 +244,7 @@
     <t>us/en/ivs/treatments/vertebroplasty</t>
   </si>
   <si>
-    <t>2026-09-10T08:34:58.326Z</t>
+    <t>2026-09-11T11:41:16.840Z</t>
   </si>
   <si>
     <t>Vertebroplasty | Interventional Spine | Stryker</t>
